--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.5</v>
+        <v>31.2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.2</v>
+        <v>30.9</v>
       </c>
       <c r="E2" t="n">
         <v>-0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>35.5</v>
+        <v>39.9</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.98</v>
+        <v>-0.96</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>-0.02</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>32.7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.7</v>
+        <v>32.4</v>
       </c>
       <c r="E3" t="n">
         <v>-0.3</v>
       </c>
       <c r="F3" t="n">
-        <v>35.5</v>
+        <v>39.9</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.92</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>-0.02</v>
       </c>
       <c r="I3" t="n">
         <v>-0</v>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34</v>
+        <v>34.7</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.7</v>
+        <v>34.4</v>
       </c>
       <c r="E4" t="n">
         <v>-0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>35.5</v>
+        <v>39.9</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.88</v>
+        <v>-0.86</v>
       </c>
       <c r="H4" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I4" t="n">
         <v>-0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.3</v>
+        <v>29.9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="E5" t="n">
         <v>-0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>35.5</v>
+        <v>39.9</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.02</v>
+        <v>-1</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,29 +500,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="F2" t="n">
-        <v>39.9</v>
+        <v>36.8</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.96</v>
+        <v>-1.28</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.30</t>
+          <t>⚠️ 非常態變動 -0.40</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="F3" t="n">
-        <v>39.9</v>
+        <v>36.8</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.92</v>
+        <v>-1.22</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I3" t="n">
         <v>-0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.30</t>
+          <t>⚠️ 非常態變動 -0.40</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="F4" t="n">
-        <v>39.9</v>
+        <v>36.8</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.86</v>
+        <v>-1.15</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.30</t>
+          <t>⚠️ 非常態變動 -0.40</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="F5" t="n">
-        <v>39.9</v>
+        <v>36.8</v>
       </c>
       <c r="G5" t="n">
-        <v>-1</v>
+        <v>-1.34</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.30</t>
+          <t>⚠️ 非常態變動 -0.40</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -506,7 +506,7 @@
         <v>-0.4</v>
       </c>
       <c r="F2" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="G2" t="n">
         <v>-1.28</v>
@@ -547,7 +547,7 @@
         <v>-0.4</v>
       </c>
       <c r="F3" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="G3" t="n">
         <v>-1.22</v>
@@ -588,13 +588,13 @@
         <v>-0.4</v>
       </c>
       <c r="F4" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="G4" t="n">
         <v>-1.15</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
@@ -629,13 +629,13 @@
         <v>-0.4</v>
       </c>
       <c r="F5" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="G5" t="n">
         <v>-1.34</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.8</v>
+        <v>31.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>36.6</v>
+        <v>39.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.28</v>
+        <v>0.96</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.40</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.3</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F3" t="n">
-        <v>36.6</v>
+        <v>39.1</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.22</v>
+        <v>0.92</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>-0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.40</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34.3</v>
+        <v>35</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>36.6</v>
+        <v>39.1</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.15</v>
+        <v>0.86</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.40</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.5</v>
+        <v>30.2</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>36.6</v>
+        <v>39.1</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.34</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.03</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.40</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.5</v>
+        <v>31.1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.96</v>
+        <v>-0.32</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.30</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>32.6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.92</v>
+        <v>-0.31</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="I3" t="n">
         <v>-0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.30</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>34.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.86</v>
+        <v>-0.29</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.30</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.2</v>
+        <v>29.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>-0.33</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.30</t>
+          <t>⚠️ 非常態變動 -0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>39.3</v>
+        <v>37.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>39.3</v>
+        <v>37.3</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.31</v>
+        <v>0.31</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I3" t="n">
         <v>-0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34.6</v>
+        <v>34.8</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>39.3</v>
+        <v>37.3</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.29</v>
+        <v>0.29</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>39.3</v>
+        <v>37.3</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.33</v>
+        <v>0.33</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>-0.02</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 -0.10</t>
+          <t>⚠️ 非常態變動 0.10</t>
         </is>
       </c>
     </row>

--- a/週五精準預測成果/FINAL_DECISION_RAW.xlsx
+++ b/週五精準預測成果/FINAL_DECISION_RAW.xlsx
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>37.3</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>0.32</v>
+        <v>0.96</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -522,7 +522,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F3" t="n">
-        <v>37.3</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I3" t="n">
         <v>-0</v>
@@ -563,7 +563,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>37.3</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>0.29</v>
+        <v>0.86</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
@@ -604,7 +604,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>37.3</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ 非常態變動 0.10</t>
+          <t>⚠️ 非常態變動 0.30</t>
         </is>
       </c>
     </row>
